--- a/Теги канала.xlsx
+++ b/Теги канала.xlsx
@@ -12,12 +12,14 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
   </bookViews>
   <sheets>
-    <sheet name="Теги канала" sheetId="1" r:id="rId1"/>
-    <sheet name="Теги канала (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId3"/>
+    <sheet name="Теги канала" sheetId="4" r:id="rId1"/>
+    <sheet name="архив " sheetId="1" r:id="rId2"/>
+    <sheet name="исходник" sheetId="3" r:id="rId3"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Теги канала'!$A$1:$C$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'архив '!$A$1:$C$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Теги канала'!$A$1:$C$158</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="701">
   <si>
     <t>#1C                                - 1C</t>
   </si>
@@ -1036,6 +1038,9 @@
     <t>Computer-Aided Engineering, АСНИ</t>
   </si>
   <si>
+    <t>AI_Gemini  </t>
+  </si>
+  <si>
     <t>AI Gemini  </t>
   </si>
   <si>
@@ -1568,13 +1573,574 @@
   </si>
   <si>
     <t>ИИ для пользователя</t>
+  </si>
+  <si>
+    <t>1C                                </t>
+  </si>
+  <si>
+    <t>3DPrint                       </t>
+  </si>
+  <si>
+    <t>3DPrintRU                  </t>
+  </si>
+  <si>
+    <t>5G                                </t>
+  </si>
+  <si>
+    <t>AbstractThinking       </t>
+  </si>
+  <si>
+    <t>AGI                              </t>
+  </si>
+  <si>
+    <t>AI                                 </t>
+  </si>
+  <si>
+    <t>AI_ChatGPT                 </t>
+  </si>
+  <si>
+    <t>AI_Claude                     </t>
+  </si>
+  <si>
+    <t>AI_DeepSeek              </t>
+  </si>
+  <si>
+    <t>AI_Grok                       </t>
+  </si>
+  <si>
+    <t>AI_Video                     </t>
+  </si>
+  <si>
+    <t>AI_Visual                     </t>
+  </si>
+  <si>
+    <t>AIagent                       </t>
+  </si>
+  <si>
+    <t>AIBusines                    </t>
+  </si>
+  <si>
+    <t>AIRU                            </t>
+  </si>
+  <si>
+    <t>AIUser                         </t>
+  </si>
+  <si>
+    <t>Analytics                     </t>
+  </si>
+  <si>
+    <t>AR                                </t>
+  </si>
+  <si>
+    <t>Automation                 </t>
+  </si>
+  <si>
+    <t>Azure                            </t>
+  </si>
+  <si>
+    <t>B2B                               </t>
+  </si>
+  <si>
+    <t>B2C                               </t>
+  </si>
+  <si>
+    <t>Bank                             </t>
+  </si>
+  <si>
+    <t>Bioeconomics               </t>
+  </si>
+  <si>
+    <t>Biometrics                    </t>
+  </si>
+  <si>
+    <t>BioTech                         </t>
+  </si>
+  <si>
+    <t>BisArch                          </t>
+  </si>
+  <si>
+    <t>BisEcoSystem                </t>
+  </si>
+  <si>
+    <t>BIZBOK                           </t>
+  </si>
+  <si>
+    <t>BlockChain                     </t>
+  </si>
+  <si>
+    <t>BPM                                </t>
+  </si>
+  <si>
+    <t>Busines                           </t>
+  </si>
+  <si>
+    <t>BusinessMethodology  </t>
+  </si>
+  <si>
+    <t>BusinessService             </t>
+  </si>
+  <si>
+    <t>BusinesUSSR                  </t>
+  </si>
+  <si>
+    <t>CAD                                </t>
+  </si>
+  <si>
+    <t>CAE                                  </t>
+  </si>
+  <si>
+    <t>CAS   </t>
+  </si>
+  <si>
+    <t>CBDC                              </t>
+  </si>
+  <si>
+    <t>Cloud                             </t>
+  </si>
+  <si>
+    <t>CloudRU                        </t>
+  </si>
+  <si>
+    <t>CodeDevelopment       </t>
+  </si>
+  <si>
+    <t>Communications          </t>
+  </si>
+  <si>
+    <t>ConsBusines                 </t>
+  </si>
+  <si>
+    <t>Consult                         </t>
+  </si>
+  <si>
+    <t>Consumers                   </t>
+  </si>
+  <si>
+    <t>CPU                               </t>
+  </si>
+  <si>
+    <t>CRM                              </t>
+  </si>
+  <si>
+    <t>CryptCurr                     </t>
+  </si>
+  <si>
+    <t>CV                                 </t>
+  </si>
+  <si>
+    <t>DataManag                  </t>
+  </si>
+  <si>
+    <t>Davos                            </t>
+  </si>
+  <si>
+    <t>DBMS                           </t>
+  </si>
+  <si>
+    <t>Dig1984                       </t>
+  </si>
+  <si>
+    <t>DigEc                           </t>
+  </si>
+  <si>
+    <t>DigEdu                        </t>
+  </si>
+  <si>
+    <t>DigitalArt                    </t>
+  </si>
+  <si>
+    <t>DigitalCulture             </t>
+  </si>
+  <si>
+    <t>Digitalization</t>
+  </si>
+  <si>
+    <t>DigitalTwin                  </t>
+  </si>
+  <si>
+    <t>DigJurisp                      </t>
+  </si>
+  <si>
+    <t>DigPay                         </t>
+  </si>
+  <si>
+    <t>DigPlatform                </t>
+  </si>
+  <si>
+    <t>DigSociety                  </t>
+  </si>
+  <si>
+    <t>DigState                      </t>
+  </si>
+  <si>
+    <t>DigTransform</t>
+  </si>
+  <si>
+    <t>Discussion                   </t>
+  </si>
+  <si>
+    <t>Dron                            </t>
+  </si>
+  <si>
+    <t>EAM                            </t>
+  </si>
+  <si>
+    <t>Ecology                       </t>
+  </si>
+  <si>
+    <t>Economy                    </t>
+  </si>
+  <si>
+    <t>EconomyHistory       </t>
+  </si>
+  <si>
+    <t>EDM_HR                    </t>
+  </si>
+  <si>
+    <t>EDMS                         </t>
+  </si>
+  <si>
+    <t>EGov                           </t>
+  </si>
+  <si>
+    <t>EHSM                         </t>
+  </si>
+  <si>
+    <t>Encryption                  </t>
+  </si>
+  <si>
+    <t>Engineering                </t>
+  </si>
+  <si>
+    <t>EnterpriseArch           </t>
+  </si>
+  <si>
+    <t>EnterpriseSoft            </t>
+  </si>
+  <si>
+    <t>ERP                              </t>
+  </si>
+  <si>
+    <t>ERPRU                          </t>
+  </si>
+  <si>
+    <t>ESB                               </t>
+  </si>
+  <si>
+    <t>ESG   </t>
+  </si>
+  <si>
+    <t>ESM                             </t>
+  </si>
+  <si>
+    <t>EWM                           </t>
+  </si>
+  <si>
+    <t>Finance                        </t>
+  </si>
+  <si>
+    <t>FinTech                        </t>
+  </si>
+  <si>
+    <t>Forecast                       </t>
+  </si>
+  <si>
+    <t>Gadgets                       </t>
+  </si>
+  <si>
+    <t>Galaktika                     </t>
+  </si>
+  <si>
+    <t>GIS                               </t>
+  </si>
+  <si>
+    <t>GlobeBusines              </t>
+  </si>
+  <si>
+    <t>Google                         </t>
+  </si>
+  <si>
+    <t>GPS                              </t>
+  </si>
+  <si>
+    <t>GreatDepression2      </t>
+  </si>
+  <si>
+    <t>Health                         </t>
+  </si>
+  <si>
+    <t>HRM                            </t>
+  </si>
+  <si>
+    <t>Ich                                </t>
+  </si>
+  <si>
+    <t>Ideas                            </t>
+  </si>
+  <si>
+    <t>Identification              </t>
+  </si>
+  <si>
+    <t>Industry4                     </t>
+  </si>
+  <si>
+    <t>Industry5                     </t>
+  </si>
+  <si>
+    <t>IndustryAgriculture      </t>
+  </si>
+  <si>
+    <t>IndustryAutomotive    </t>
+  </si>
+  <si>
+    <t>IndustryConstruction </t>
+  </si>
+  <si>
+    <t>IndustryForestry         </t>
+  </si>
+  <si>
+    <t>IndustryMetallurgy    </t>
+  </si>
+  <si>
+    <t>IndustryMining          </t>
+  </si>
+  <si>
+    <t>IndustryOilGas            </t>
+  </si>
+  <si>
+    <t>IndustryTelecom        </t>
+  </si>
+  <si>
+    <t>IndustryTrading         </t>
+  </si>
+  <si>
+    <t>IndustryTransport     </t>
+  </si>
+  <si>
+    <t>Info                             </t>
+  </si>
+  <si>
+    <t>Innovations                </t>
+  </si>
+  <si>
+    <t>Internet                      </t>
+  </si>
+  <si>
+    <t>Invention                   </t>
+  </si>
+  <si>
+    <t>IoB                              </t>
+  </si>
+  <si>
+    <t>IoT                              </t>
+  </si>
+  <si>
+    <t>IT                                </t>
+  </si>
+  <si>
+    <t>ITArchitect                 </t>
+  </si>
+  <si>
+    <t>ITBusines                   </t>
+  </si>
+  <si>
+    <t>ITBusinesUSSR          </t>
+  </si>
+  <si>
+    <t>ITcomponents           </t>
+  </si>
+  <si>
+    <t>ITInfrastructure        </t>
+  </si>
+  <si>
+    <t>ITJurisprudence       </t>
+  </si>
+  <si>
+    <t>ITReliability              </t>
+  </si>
+  <si>
+    <t>ITSM                         </t>
+  </si>
+  <si>
+    <t>KnowledgeGraph    </t>
+  </si>
+  <si>
+    <t>Life                             </t>
+  </si>
+  <si>
+    <t>Logistics                    </t>
+  </si>
+  <si>
+    <t>MaintenanceRepairs </t>
+  </si>
+  <si>
+    <t>Management            </t>
+  </si>
+  <si>
+    <t>Marketing                 </t>
+  </si>
+  <si>
+    <t>MarketPlace              </t>
+  </si>
+  <si>
+    <t>Math                           </t>
+  </si>
+  <si>
+    <t>MDM                         </t>
+  </si>
+  <si>
+    <t>MemoryChip             </t>
+  </si>
+  <si>
+    <t>MES                           </t>
+  </si>
+  <si>
+    <t>Messenger                </t>
+  </si>
+  <si>
+    <t>Microsoft                  </t>
+  </si>
+  <si>
+    <t>ML                              </t>
+  </si>
+  <si>
+    <t>Money                       </t>
+  </si>
+  <si>
+    <t>NewEnergy               </t>
+  </si>
+  <si>
+    <t>NewMaterials           </t>
+  </si>
+  <si>
+    <t>NewReality                  </t>
+  </si>
+  <si>
+    <t>NewTechnolog          </t>
+  </si>
+  <si>
+    <t>NobelPrize                 </t>
+  </si>
+  <si>
+    <t>OCR                             </t>
+  </si>
+  <si>
+    <t>Office                           </t>
+  </si>
+  <si>
+    <t>OnlineStore                  </t>
+  </si>
+  <si>
+    <t>OODA                          </t>
+  </si>
+  <si>
+    <t>Oracle                            </t>
+  </si>
+  <si>
+    <t>OS                               </t>
+  </si>
+  <si>
+    <t>Procurement              </t>
+  </si>
+  <si>
+    <t>Production                  </t>
+  </si>
+  <si>
+    <t>ProjectManagement </t>
+  </si>
+  <si>
+    <t>Psycho                        </t>
+  </si>
+  <si>
+    <t>Quality                        </t>
+  </si>
+  <si>
+    <t>QuantumComputing </t>
+  </si>
+  <si>
+    <t>RandD                           </t>
+  </si>
+  <si>
+    <t>Regulation                    </t>
+  </si>
+  <si>
+    <t>Results                         </t>
+  </si>
+  <si>
+    <t>#AI_Kimi</t>
+  </si>
+  <si>
+    <t>ИИ Kimi</t>
+  </si>
+  <si>
+    <t>#AI_Video</t>
+  </si>
+  <si>
+    <t>#AI_Visual</t>
+  </si>
+  <si>
+    <t>#AIagent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ИИ агенты </t>
+  </si>
+  <si>
+    <t>#AISecretary</t>
+  </si>
+  <si>
+    <t>ИИ личный секретарь</t>
+  </si>
+  <si>
+    <t>#BusinessService</t>
+  </si>
+  <si>
+    <t>бизнес-услуги</t>
+  </si>
+  <si>
+    <t>#FreeSoftware</t>
+  </si>
+  <si>
+    <t>свободное программное обеспечение</t>
+  </si>
+  <si>
+    <t>#Galaktika</t>
+  </si>
+  <si>
+    <t>ERP Галактика</t>
+  </si>
+  <si>
+    <t>#GIS</t>
+  </si>
+  <si>
+    <t>#Governance</t>
+  </si>
+  <si>
+    <t>управление через регулирование</t>
+  </si>
+  <si>
+    <t>#Intranet</t>
+  </si>
+  <si>
+    <t>интранет</t>
+  </si>
+  <si>
+    <t>#Neurointerfaces</t>
+  </si>
+  <si>
+    <t>нейроинтерфесы</t>
+  </si>
+  <si>
+    <t>#Risk</t>
+  </si>
+  <si>
+    <t>риск</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1595,6 +2161,29 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFEE0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFEE0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
@@ -1626,7 +2215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1636,6 +2225,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1916,6 +2517,1440 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B177"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="2" max="2" width="53.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B11" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B13" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>678</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B16" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>170</v>
+      </c>
+      <c r="B18" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>174</v>
+      </c>
+      <c r="B20" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>173</v>
+      </c>
+      <c r="B21" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>171</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>684</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>172</v>
+      </c>
+      <c r="B24" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>175</v>
+      </c>
+      <c r="B25" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>176</v>
+      </c>
+      <c r="B26" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>177</v>
+      </c>
+      <c r="B27" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>178</v>
+      </c>
+      <c r="B28" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>179</v>
+      </c>
+      <c r="B29" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>180</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>181</v>
+      </c>
+      <c r="B31" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>184</v>
+      </c>
+      <c r="B32" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>182</v>
+      </c>
+      <c r="B33" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>183</v>
+      </c>
+      <c r="B34" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>185</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>186</v>
+      </c>
+      <c r="B36" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>187</v>
+      </c>
+      <c r="B37" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>188</v>
+      </c>
+      <c r="B38" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>189</v>
+      </c>
+      <c r="B39" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>190</v>
+      </c>
+      <c r="B40" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>191</v>
+      </c>
+      <c r="B41" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>193</v>
+      </c>
+      <c r="B43" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>194</v>
+      </c>
+      <c r="B44" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>323</v>
+      </c>
+      <c r="B45" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>322</v>
+      </c>
+      <c r="B46" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>195</v>
+      </c>
+      <c r="B47" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>196</v>
+      </c>
+      <c r="B48" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>197</v>
+      </c>
+      <c r="B49" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>198</v>
+      </c>
+      <c r="B50" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>199</v>
+      </c>
+      <c r="B51" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>200</v>
+      </c>
+      <c r="B52" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>201</v>
+      </c>
+      <c r="B53" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>202</v>
+      </c>
+      <c r="B54" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>203</v>
+      </c>
+      <c r="B55" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>204</v>
+      </c>
+      <c r="B56" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>205</v>
+      </c>
+      <c r="B57" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>206</v>
+      </c>
+      <c r="B58" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>207</v>
+      </c>
+      <c r="B59" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>208</v>
+      </c>
+      <c r="B60" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>209</v>
+      </c>
+      <c r="B61" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>210</v>
+      </c>
+      <c r="B62" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>213</v>
+      </c>
+      <c r="B63" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>214</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>211</v>
+      </c>
+      <c r="B65" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>212</v>
+      </c>
+      <c r="B66" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>216</v>
+      </c>
+      <c r="B67" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>222</v>
+      </c>
+      <c r="B68" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>215</v>
+      </c>
+      <c r="B69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>217</v>
+      </c>
+      <c r="B70" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>218</v>
+      </c>
+      <c r="B71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>219</v>
+      </c>
+      <c r="B72" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>220</v>
+      </c>
+      <c r="B73" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>221</v>
+      </c>
+      <c r="B74" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>223</v>
+      </c>
+      <c r="B75" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>224</v>
+      </c>
+      <c r="B76" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>225</v>
+      </c>
+      <c r="B77" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>226</v>
+      </c>
+      <c r="B78" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>227</v>
+      </c>
+      <c r="B79" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>228</v>
+      </c>
+      <c r="B80" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>230</v>
+      </c>
+      <c r="B81" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>231</v>
+      </c>
+      <c r="B82" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>229</v>
+      </c>
+      <c r="B83" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>232</v>
+      </c>
+      <c r="B84" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>233</v>
+      </c>
+      <c r="B85" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>269</v>
+      </c>
+      <c r="B86" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>235</v>
+      </c>
+      <c r="B87" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>234</v>
+      </c>
+      <c r="B88" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>236</v>
+      </c>
+      <c r="B89" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>237</v>
+      </c>
+      <c r="B90" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>238</v>
+      </c>
+      <c r="B91" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>330</v>
+      </c>
+      <c r="B92" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>239</v>
+      </c>
+      <c r="B93" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>240</v>
+      </c>
+      <c r="B94" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>241</v>
+      </c>
+      <c r="B95" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>242</v>
+      </c>
+      <c r="B96" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>243</v>
+      </c>
+      <c r="B97" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>244</v>
+      </c>
+      <c r="B99" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="B100" s="10" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="B101" s="10" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>246</v>
+      </c>
+      <c r="B102" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>247</v>
+      </c>
+      <c r="B103" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>248</v>
+      </c>
+      <c r="B104" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>249</v>
+      </c>
+      <c r="B106" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>250</v>
+      </c>
+      <c r="B107" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>251</v>
+      </c>
+      <c r="B108" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>252</v>
+      </c>
+      <c r="B109" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>253</v>
+      </c>
+      <c r="B110" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>254</v>
+      </c>
+      <c r="B111" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>255</v>
+      </c>
+      <c r="B112" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>256</v>
+      </c>
+      <c r="B113" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>257</v>
+      </c>
+      <c r="B114" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>258</v>
+      </c>
+      <c r="B115" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>259</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>260</v>
+      </c>
+      <c r="B117" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>261</v>
+      </c>
+      <c r="B118" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>262</v>
+      </c>
+      <c r="B119" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>263</v>
+      </c>
+      <c r="B120" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>264</v>
+      </c>
+      <c r="B121" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>265</v>
+      </c>
+      <c r="B122" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>266</v>
+      </c>
+      <c r="B123" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>267</v>
+      </c>
+      <c r="B124" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>268</v>
+      </c>
+      <c r="B125" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>270</v>
+      </c>
+      <c r="B126" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>271</v>
+      </c>
+      <c r="B127" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" s="7" t="s">
+        <v>695</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>272</v>
+      </c>
+      <c r="B129" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>273</v>
+      </c>
+      <c r="B130" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>274</v>
+      </c>
+      <c r="B131" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>275</v>
+      </c>
+      <c r="B132" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>276</v>
+      </c>
+      <c r="B133" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>277</v>
+      </c>
+      <c r="B134" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>278</v>
+      </c>
+      <c r="B135" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>279</v>
+      </c>
+      <c r="B136" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>280</v>
+      </c>
+      <c r="B137" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>281</v>
+      </c>
+      <c r="B138" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>282</v>
+      </c>
+      <c r="B139" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>283</v>
+      </c>
+      <c r="B140" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>284</v>
+      </c>
+      <c r="B141" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>285</v>
+      </c>
+      <c r="B142" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>286</v>
+      </c>
+      <c r="B143" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>287</v>
+      </c>
+      <c r="B144" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>288</v>
+      </c>
+      <c r="B145" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>289</v>
+      </c>
+      <c r="B146" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>290</v>
+      </c>
+      <c r="B147" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>291</v>
+      </c>
+      <c r="B148" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>292</v>
+      </c>
+      <c r="B149" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>293</v>
+      </c>
+      <c r="B150" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>294</v>
+      </c>
+      <c r="B151" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>295</v>
+      </c>
+      <c r="B152" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>296</v>
+      </c>
+      <c r="B153" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>297</v>
+      </c>
+      <c r="B154" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>298</v>
+      </c>
+      <c r="B155" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" s="7" t="s">
+        <v>697</v>
+      </c>
+      <c r="B156" s="8" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>299</v>
+      </c>
+      <c r="B157" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>300</v>
+      </c>
+      <c r="B158" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>301</v>
+      </c>
+      <c r="B159" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>302</v>
+      </c>
+      <c r="B160" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>303</v>
+      </c>
+      <c r="B161" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>304</v>
+      </c>
+      <c r="B162" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>305</v>
+      </c>
+      <c r="B163" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>312</v>
+      </c>
+      <c r="B164" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>306</v>
+      </c>
+      <c r="B165" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>313</v>
+      </c>
+      <c r="B166" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>307</v>
+      </c>
+      <c r="B167" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>309</v>
+      </c>
+      <c r="B168" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>310</v>
+      </c>
+      <c r="B169" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>308</v>
+      </c>
+      <c r="B170" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>311</v>
+      </c>
+      <c r="B171" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>315</v>
+      </c>
+      <c r="B172" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>314</v>
+      </c>
+      <c r="B173" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>316</v>
+      </c>
+      <c r="B174" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>317</v>
+      </c>
+      <c r="B175" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>318</v>
+      </c>
+      <c r="B176" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" s="7" t="s">
+        <v>699</v>
+      </c>
+      <c r="B177" s="8" t="s">
+        <v>700</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A2:B185">
+    <sortCondition ref="A2:A185"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B166"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1933,311 +3968,311 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>158</v>
+        <v>514</v>
       </c>
       <c r="B2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>515</v>
       </c>
       <c r="B3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>160</v>
+        <v>516</v>
       </c>
       <c r="B4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>159</v>
+        <v>517</v>
       </c>
       <c r="B5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>162</v>
+        <v>518</v>
       </c>
       <c r="B6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>163</v>
+        <v>519</v>
       </c>
       <c r="B7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>164</v>
+        <v>520</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>165</v>
+        <v>521</v>
       </c>
       <c r="B9" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>166</v>
+        <v>522</v>
       </c>
       <c r="B10" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>167</v>
+        <v>523</v>
       </c>
       <c r="B11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>157</v>
+        <v>335</v>
       </c>
       <c r="B12" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>168</v>
+        <v>524</v>
       </c>
       <c r="B13" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>169</v>
+        <v>525</v>
       </c>
       <c r="B14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>170</v>
+        <v>526</v>
       </c>
       <c r="B15" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>174</v>
+        <v>527</v>
       </c>
       <c r="B16" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>173</v>
+        <v>528</v>
       </c>
       <c r="B17" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>171</v>
+        <v>529</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>172</v>
+        <v>530</v>
       </c>
       <c r="B19" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>175</v>
+        <v>531</v>
       </c>
       <c r="B20" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>176</v>
+        <v>532</v>
       </c>
       <c r="B21" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>177</v>
+        <v>533</v>
       </c>
       <c r="B22" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>178</v>
+        <v>534</v>
       </c>
       <c r="B23" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>179</v>
+        <v>535</v>
       </c>
       <c r="B24" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>180</v>
+        <v>536</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>181</v>
+        <v>537</v>
       </c>
       <c r="B26" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>184</v>
+        <v>538</v>
       </c>
       <c r="B27" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>182</v>
+        <v>539</v>
       </c>
       <c r="B28" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>183</v>
+        <v>540</v>
       </c>
       <c r="B29" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>185</v>
+        <v>541</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>186</v>
+        <v>542</v>
       </c>
       <c r="B31" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>187</v>
+        <v>543</v>
       </c>
       <c r="B32" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>188</v>
+        <v>544</v>
       </c>
       <c r="B33" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>189</v>
+        <v>545</v>
       </c>
       <c r="B34" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>190</v>
+        <v>546</v>
       </c>
       <c r="B35" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>191</v>
+        <v>547</v>
       </c>
       <c r="B36" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>192</v>
+        <v>548</v>
       </c>
       <c r="B37" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>193</v>
+        <v>549</v>
       </c>
       <c r="B38" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>194</v>
+        <v>550</v>
       </c>
       <c r="B39" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>323</v>
+        <v>551</v>
       </c>
       <c r="B40" t="s">
         <v>334</v>
@@ -2245,1010 +4280,1010 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>322</v>
+        <v>552</v>
       </c>
       <c r="B41" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>195</v>
+        <v>553</v>
       </c>
       <c r="B42" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>196</v>
+        <v>554</v>
       </c>
       <c r="B43" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>197</v>
+        <v>555</v>
       </c>
       <c r="B44" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>198</v>
+        <v>556</v>
       </c>
       <c r="B45" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>199</v>
+        <v>557</v>
       </c>
       <c r="B46" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>200</v>
+        <v>558</v>
       </c>
       <c r="B47" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>201</v>
+        <v>559</v>
       </c>
       <c r="B48" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>202</v>
+        <v>560</v>
       </c>
       <c r="B49" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>203</v>
+        <v>561</v>
       </c>
       <c r="B50" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>204</v>
+        <v>562</v>
       </c>
       <c r="B51" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>205</v>
+        <v>563</v>
       </c>
       <c r="B52" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>206</v>
+        <v>564</v>
       </c>
       <c r="B53" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>207</v>
+        <v>565</v>
       </c>
       <c r="B54" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>208</v>
+        <v>566</v>
       </c>
       <c r="B55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>209</v>
+        <v>567</v>
       </c>
       <c r="B56" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>210</v>
+        <v>568</v>
       </c>
       <c r="B57" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>213</v>
+        <v>569</v>
       </c>
       <c r="B58" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>214</v>
+        <v>570</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>211</v>
+        <v>571</v>
       </c>
       <c r="B60" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>212</v>
+        <v>572</v>
       </c>
       <c r="B61" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>216</v>
+        <v>573</v>
       </c>
       <c r="B62" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>222</v>
+        <v>574</v>
       </c>
       <c r="B63" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>215</v>
+        <v>575</v>
       </c>
       <c r="B64" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>217</v>
+        <v>576</v>
       </c>
       <c r="B65" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>218</v>
+        <v>577</v>
       </c>
       <c r="B66" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>219</v>
+        <v>578</v>
       </c>
       <c r="B67" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>220</v>
+        <v>579</v>
       </c>
       <c r="B68" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>221</v>
+        <v>580</v>
       </c>
       <c r="B69" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>223</v>
+        <v>581</v>
       </c>
       <c r="B70" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>224</v>
+        <v>582</v>
       </c>
       <c r="B71" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>225</v>
+        <v>583</v>
       </c>
       <c r="B72" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>226</v>
+        <v>584</v>
       </c>
       <c r="B73" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>227</v>
+        <v>585</v>
       </c>
       <c r="B74" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>228</v>
+        <v>586</v>
       </c>
       <c r="B75" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>230</v>
+        <v>587</v>
       </c>
       <c r="B76" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>231</v>
+        <v>588</v>
       </c>
       <c r="B77" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>229</v>
+        <v>589</v>
       </c>
       <c r="B78" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>232</v>
+        <v>590</v>
       </c>
       <c r="B79" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>233</v>
+        <v>591</v>
       </c>
       <c r="B80" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>269</v>
+        <v>592</v>
       </c>
       <c r="B81" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>235</v>
+        <v>593</v>
       </c>
       <c r="B82" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>234</v>
+        <v>594</v>
       </c>
       <c r="B83" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>236</v>
+        <v>595</v>
       </c>
       <c r="B84" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>237</v>
+        <v>596</v>
       </c>
       <c r="B85" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>238</v>
+        <v>597</v>
       </c>
       <c r="B86" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>330</v>
+        <v>598</v>
       </c>
       <c r="B87" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>239</v>
+        <v>599</v>
       </c>
       <c r="B88" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>240</v>
+        <v>600</v>
       </c>
       <c r="B89" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>241</v>
+        <v>601</v>
       </c>
       <c r="B90" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>242</v>
+        <v>602</v>
       </c>
       <c r="B91" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>243</v>
+        <v>603</v>
       </c>
       <c r="B92" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>244</v>
+        <v>604</v>
       </c>
       <c r="B93" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>245</v>
+        <v>605</v>
       </c>
       <c r="B94" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>246</v>
+        <v>606</v>
       </c>
       <c r="B95" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>247</v>
+        <v>607</v>
       </c>
       <c r="B96" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>248</v>
+        <v>608</v>
       </c>
       <c r="B97" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>249</v>
+        <v>609</v>
       </c>
       <c r="B98" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>250</v>
+        <v>610</v>
       </c>
       <c r="B99" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>251</v>
+        <v>611</v>
       </c>
       <c r="B100" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>252</v>
+        <v>612</v>
       </c>
       <c r="B101" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>253</v>
+        <v>613</v>
       </c>
       <c r="B102" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>254</v>
+        <v>614</v>
       </c>
       <c r="B103" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>255</v>
+        <v>615</v>
       </c>
       <c r="B104" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>256</v>
+        <v>616</v>
       </c>
       <c r="B105" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>257</v>
+        <v>617</v>
       </c>
       <c r="B106" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>258</v>
+        <v>618</v>
       </c>
       <c r="B107" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>259</v>
+        <v>619</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>260</v>
+        <v>620</v>
       </c>
       <c r="B109" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>261</v>
+        <v>621</v>
       </c>
       <c r="B110" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>262</v>
+        <v>622</v>
       </c>
       <c r="B111" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>263</v>
+        <v>623</v>
       </c>
       <c r="B112" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>264</v>
+        <v>624</v>
       </c>
       <c r="B113" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>265</v>
+        <v>625</v>
       </c>
       <c r="B114" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>266</v>
+        <v>626</v>
       </c>
       <c r="B115" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>267</v>
+        <v>627</v>
       </c>
       <c r="B116" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>268</v>
+        <v>628</v>
       </c>
       <c r="B117" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>270</v>
+        <v>629</v>
       </c>
       <c r="B118" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>271</v>
+        <v>630</v>
       </c>
       <c r="B119" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>272</v>
+        <v>631</v>
       </c>
       <c r="B120" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>273</v>
+        <v>632</v>
       </c>
       <c r="B121" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>274</v>
+        <v>633</v>
       </c>
       <c r="B122" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>275</v>
+        <v>634</v>
       </c>
       <c r="B123" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>276</v>
+        <v>635</v>
       </c>
       <c r="B124" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>277</v>
+        <v>636</v>
       </c>
       <c r="B125" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>278</v>
+        <v>637</v>
       </c>
       <c r="B126" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>279</v>
+        <v>638</v>
       </c>
       <c r="B127" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>280</v>
+        <v>639</v>
       </c>
       <c r="B128" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>281</v>
+        <v>640</v>
       </c>
       <c r="B129" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>282</v>
+        <v>641</v>
       </c>
       <c r="B130" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>283</v>
+        <v>642</v>
       </c>
       <c r="B131" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>284</v>
+        <v>643</v>
       </c>
       <c r="B132" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>285</v>
+        <v>644</v>
       </c>
       <c r="B133" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>286</v>
+        <v>645</v>
       </c>
       <c r="B134" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>287</v>
+        <v>646</v>
       </c>
       <c r="B135" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>288</v>
+        <v>647</v>
       </c>
       <c r="B136" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>289</v>
+        <v>648</v>
       </c>
       <c r="B137" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>290</v>
+        <v>649</v>
       </c>
       <c r="B138" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>291</v>
+        <v>650</v>
       </c>
       <c r="B139" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>292</v>
+        <v>651</v>
       </c>
       <c r="B140" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>293</v>
+        <v>652</v>
       </c>
       <c r="B141" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>294</v>
+        <v>653</v>
       </c>
       <c r="B142" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>295</v>
+        <v>654</v>
       </c>
       <c r="B143" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>296</v>
+        <v>655</v>
       </c>
       <c r="B144" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>297</v>
+        <v>656</v>
       </c>
       <c r="B145" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>298</v>
+        <v>657</v>
       </c>
       <c r="B146" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>299</v>
+        <v>658</v>
       </c>
       <c r="B147" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>300</v>
+        <v>659</v>
       </c>
       <c r="B148" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>301</v>
+        <v>660</v>
       </c>
       <c r="B149" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>302</v>
+        <v>661</v>
       </c>
       <c r="B150" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>303</v>
+        <v>662</v>
       </c>
       <c r="B151" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>304</v>
+        <v>663</v>
       </c>
       <c r="B152" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>305</v>
+        <v>664</v>
       </c>
       <c r="B153" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>312</v>
+        <v>665</v>
       </c>
       <c r="B154" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>306</v>
+        <v>666</v>
       </c>
       <c r="B155" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>313</v>
+        <v>667</v>
       </c>
       <c r="B156" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>307</v>
+        <v>668</v>
       </c>
       <c r="B157" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>309</v>
+        <v>669</v>
       </c>
       <c r="B158" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>310</v>
+        <v>670</v>
       </c>
       <c r="B159" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>308</v>
+        <v>671</v>
       </c>
       <c r="B160" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>311</v>
+        <v>672</v>
       </c>
       <c r="B161" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>315</v>
+        <v>673</v>
       </c>
       <c r="B162" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>314</v>
+        <v>674</v>
       </c>
       <c r="B163" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>316</v>
+        <v>675</v>
       </c>
       <c r="B164" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>317</v>
+        <v>676</v>
       </c>
       <c r="B165" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>318</v>
+        <v>677</v>
       </c>
       <c r="B166" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
   </sheetData>
@@ -3261,7 +5296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C166"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3290,7 +5325,7 @@
         <v>158</v>
       </c>
       <c r="C2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -3301,7 +5336,7 @@
         <v>159</v>
       </c>
       <c r="C3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -3312,7 +5347,7 @@
         <v>160</v>
       </c>
       <c r="C4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -3323,7 +5358,7 @@
         <v>161</v>
       </c>
       <c r="C5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -3334,7 +5369,7 @@
         <v>162</v>
       </c>
       <c r="C6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -3345,7 +5380,7 @@
         <v>163</v>
       </c>
       <c r="C7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -3356,7 +5391,7 @@
         <v>164</v>
       </c>
       <c r="C8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -3367,7 +5402,7 @@
         <v>165</v>
       </c>
       <c r="C9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -3378,7 +5413,7 @@
         <v>166</v>
       </c>
       <c r="C10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -3389,7 +5424,7 @@
         <v>167</v>
       </c>
       <c r="C11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -3400,7 +5435,7 @@
         <v>157</v>
       </c>
       <c r="C12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -3411,7 +5446,7 @@
         <v>168</v>
       </c>
       <c r="C13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -3422,7 +5457,7 @@
         <v>169</v>
       </c>
       <c r="C14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -3433,7 +5468,7 @@
         <v>170</v>
       </c>
       <c r="C15" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -3444,7 +5479,7 @@
         <v>171</v>
       </c>
       <c r="C16" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -3455,7 +5490,7 @@
         <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -3466,7 +5501,7 @@
         <v>173</v>
       </c>
       <c r="C18" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -3477,7 +5512,7 @@
         <v>174</v>
       </c>
       <c r="C19" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -3488,7 +5523,7 @@
         <v>175</v>
       </c>
       <c r="C20" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -3499,7 +5534,7 @@
         <v>176</v>
       </c>
       <c r="C21" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -3510,7 +5545,7 @@
         <v>177</v>
       </c>
       <c r="C22" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -3521,7 +5556,7 @@
         <v>178</v>
       </c>
       <c r="C23" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -3532,7 +5567,7 @@
         <v>179</v>
       </c>
       <c r="C24" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -3543,7 +5578,7 @@
         <v>180</v>
       </c>
       <c r="C25" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -3554,7 +5589,7 @@
         <v>181</v>
       </c>
       <c r="C26" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -3565,7 +5600,7 @@
         <v>182</v>
       </c>
       <c r="C27" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -3576,7 +5611,7 @@
         <v>183</v>
       </c>
       <c r="C28" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -3587,7 +5622,7 @@
         <v>184</v>
       </c>
       <c r="C29" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -3598,7 +5633,7 @@
         <v>185</v>
       </c>
       <c r="C30" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -3609,7 +5644,7 @@
         <v>186</v>
       </c>
       <c r="C31" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -3620,7 +5655,7 @@
         <v>187</v>
       </c>
       <c r="C32" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -3631,7 +5666,7 @@
         <v>188</v>
       </c>
       <c r="C33" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -3642,7 +5677,7 @@
         <v>189</v>
       </c>
       <c r="C34" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -3653,7 +5688,7 @@
         <v>190</v>
       </c>
       <c r="C35" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -3664,7 +5699,7 @@
         <v>191</v>
       </c>
       <c r="C36" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -3675,7 +5710,7 @@
         <v>192</v>
       </c>
       <c r="C37" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -3686,7 +5721,7 @@
         <v>193</v>
       </c>
       <c r="C38" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -3697,7 +5732,7 @@
         <v>194</v>
       </c>
       <c r="C39" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -3719,7 +5754,7 @@
         <v>322</v>
       </c>
       <c r="C41" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -3730,7 +5765,7 @@
         <v>195</v>
       </c>
       <c r="C42" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -3741,7 +5776,7 @@
         <v>196</v>
       </c>
       <c r="C43" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -3752,7 +5787,7 @@
         <v>197</v>
       </c>
       <c r="C44" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -3763,7 +5798,7 @@
         <v>198</v>
       </c>
       <c r="C45" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -3774,7 +5809,7 @@
         <v>199</v>
       </c>
       <c r="C46" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -3785,7 +5820,7 @@
         <v>200</v>
       </c>
       <c r="C47" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -3796,7 +5831,7 @@
         <v>201</v>
       </c>
       <c r="C48" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -3807,7 +5842,7 @@
         <v>202</v>
       </c>
       <c r="C49" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -3818,7 +5853,7 @@
         <v>203</v>
       </c>
       <c r="C50" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -3829,7 +5864,7 @@
         <v>204</v>
       </c>
       <c r="C51" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -3840,7 +5875,7 @@
         <v>205</v>
       </c>
       <c r="C52" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -3851,7 +5886,7 @@
         <v>206</v>
       </c>
       <c r="C53" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -3862,7 +5897,7 @@
         <v>207</v>
       </c>
       <c r="C54" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -3873,7 +5908,7 @@
         <v>208</v>
       </c>
       <c r="C55" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -3884,7 +5919,7 @@
         <v>209</v>
       </c>
       <c r="C56" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -3895,7 +5930,7 @@
         <v>210</v>
       </c>
       <c r="C57" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -3906,7 +5941,7 @@
         <v>211</v>
       </c>
       <c r="C58" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -3917,7 +5952,7 @@
         <v>212</v>
       </c>
       <c r="C59" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -3928,7 +5963,7 @@
         <v>213</v>
       </c>
       <c r="C60" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -3939,7 +5974,7 @@
         <v>214</v>
       </c>
       <c r="C61" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -3950,7 +5985,7 @@
         <v>215</v>
       </c>
       <c r="C62" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -3961,7 +5996,7 @@
         <v>216</v>
       </c>
       <c r="C63" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -3972,7 +6007,7 @@
         <v>217</v>
       </c>
       <c r="C64" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -3983,7 +6018,7 @@
         <v>218</v>
       </c>
       <c r="C65" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -3994,7 +6029,7 @@
         <v>219</v>
       </c>
       <c r="C66" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -4005,7 +6040,7 @@
         <v>220</v>
       </c>
       <c r="C67" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -4016,7 +6051,7 @@
         <v>221</v>
       </c>
       <c r="C68" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -4027,7 +6062,7 @@
         <v>222</v>
       </c>
       <c r="C69" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -4038,7 +6073,7 @@
         <v>223</v>
       </c>
       <c r="C70" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -4049,7 +6084,7 @@
         <v>224</v>
       </c>
       <c r="C71" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -4060,7 +6095,7 @@
         <v>225</v>
       </c>
       <c r="C72" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -4071,7 +6106,7 @@
         <v>226</v>
       </c>
       <c r="C73" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -4082,7 +6117,7 @@
         <v>227</v>
       </c>
       <c r="C74" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -4093,7 +6128,7 @@
         <v>228</v>
       </c>
       <c r="C75" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -4104,7 +6139,7 @@
         <v>229</v>
       </c>
       <c r="C76" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -4115,7 +6150,7 @@
         <v>230</v>
       </c>
       <c r="C77" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -4126,7 +6161,7 @@
         <v>231</v>
       </c>
       <c r="C78" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -4137,7 +6172,7 @@
         <v>232</v>
       </c>
       <c r="C79" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -4148,7 +6183,7 @@
         <v>233</v>
       </c>
       <c r="C80" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -4159,7 +6194,7 @@
         <v>234</v>
       </c>
       <c r="C81" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -4170,7 +6205,7 @@
         <v>235</v>
       </c>
       <c r="C82" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -4181,7 +6216,7 @@
         <v>236</v>
       </c>
       <c r="C83" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -4192,7 +6227,7 @@
         <v>237</v>
       </c>
       <c r="C84" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -4203,7 +6238,7 @@
         <v>238</v>
       </c>
       <c r="C85" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -4214,7 +6249,7 @@
         <v>330</v>
       </c>
       <c r="C86" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -4225,7 +6260,7 @@
         <v>239</v>
       </c>
       <c r="C87" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -4236,7 +6271,7 @@
         <v>240</v>
       </c>
       <c r="C88" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -4247,7 +6282,7 @@
         <v>241</v>
       </c>
       <c r="C89" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -4258,7 +6293,7 @@
         <v>242</v>
       </c>
       <c r="C90" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -4269,7 +6304,7 @@
         <v>243</v>
       </c>
       <c r="C91" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -4280,7 +6315,7 @@
         <v>244</v>
       </c>
       <c r="C92" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -4291,7 +6326,7 @@
         <v>245</v>
       </c>
       <c r="C93" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -4302,7 +6337,7 @@
         <v>246</v>
       </c>
       <c r="C94" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -4313,7 +6348,7 @@
         <v>247</v>
       </c>
       <c r="C95" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -4324,7 +6359,7 @@
         <v>248</v>
       </c>
       <c r="C96" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -4335,7 +6370,7 @@
         <v>249</v>
       </c>
       <c r="C97" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -4346,7 +6381,7 @@
         <v>250</v>
       </c>
       <c r="C98" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -4357,7 +6392,7 @@
         <v>251</v>
       </c>
       <c r="C99" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -4368,7 +6403,7 @@
         <v>252</v>
       </c>
       <c r="C100" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -4379,7 +6414,7 @@
         <v>253</v>
       </c>
       <c r="C101" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -4390,7 +6425,7 @@
         <v>254</v>
       </c>
       <c r="C102" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -4401,7 +6436,7 @@
         <v>255</v>
       </c>
       <c r="C103" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -4412,7 +6447,7 @@
         <v>256</v>
       </c>
       <c r="C104" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -4423,7 +6458,7 @@
         <v>257</v>
       </c>
       <c r="C105" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -4434,7 +6469,7 @@
         <v>258</v>
       </c>
       <c r="C106" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -4445,7 +6480,7 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -4456,7 +6491,7 @@
         <v>260</v>
       </c>
       <c r="C108" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -4467,7 +6502,7 @@
         <v>261</v>
       </c>
       <c r="C109" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -4478,7 +6513,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -4489,7 +6524,7 @@
         <v>263</v>
       </c>
       <c r="C111" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -4500,7 +6535,7 @@
         <v>264</v>
       </c>
       <c r="C112" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -4511,7 +6546,7 @@
         <v>265</v>
       </c>
       <c r="C113" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -4522,7 +6557,7 @@
         <v>266</v>
       </c>
       <c r="C114" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -4533,7 +6568,7 @@
         <v>267</v>
       </c>
       <c r="C115" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -4544,7 +6579,7 @@
         <v>268</v>
       </c>
       <c r="C116" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -4555,7 +6590,7 @@
         <v>269</v>
       </c>
       <c r="C117" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -4566,7 +6601,7 @@
         <v>270</v>
       </c>
       <c r="C118" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -4577,7 +6612,7 @@
         <v>271</v>
       </c>
       <c r="C119" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -4588,7 +6623,7 @@
         <v>272</v>
       </c>
       <c r="C120" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -4599,7 +6634,7 @@
         <v>273</v>
       </c>
       <c r="C121" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -4610,7 +6645,7 @@
         <v>274</v>
       </c>
       <c r="C122" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -4621,7 +6656,7 @@
         <v>275</v>
       </c>
       <c r="C123" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -4632,7 +6667,7 @@
         <v>276</v>
       </c>
       <c r="C124" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -4643,7 +6678,7 @@
         <v>277</v>
       </c>
       <c r="C125" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -4654,7 +6689,7 @@
         <v>278</v>
       </c>
       <c r="C126" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -4665,7 +6700,7 @@
         <v>279</v>
       </c>
       <c r="C127" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -4676,7 +6711,7 @@
         <v>280</v>
       </c>
       <c r="C128" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -4687,7 +6722,7 @@
         <v>281</v>
       </c>
       <c r="C129" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -4698,7 +6733,7 @@
         <v>282</v>
       </c>
       <c r="C130" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -4709,7 +6744,7 @@
         <v>283</v>
       </c>
       <c r="C131" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -4720,7 +6755,7 @@
         <v>284</v>
       </c>
       <c r="C132" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -4731,7 +6766,7 @@
         <v>285</v>
       </c>
       <c r="C133" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -4742,7 +6777,7 @@
         <v>286</v>
       </c>
       <c r="C134" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -4753,7 +6788,7 @@
         <v>287</v>
       </c>
       <c r="C135" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -4764,7 +6799,7 @@
         <v>288</v>
       </c>
       <c r="C136" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -4775,7 +6810,7 @@
         <v>289</v>
       </c>
       <c r="C137" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -4786,7 +6821,7 @@
         <v>290</v>
       </c>
       <c r="C138" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -4797,7 +6832,7 @@
         <v>291</v>
       </c>
       <c r="C139" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -4808,7 +6843,7 @@
         <v>292</v>
       </c>
       <c r="C140" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -4819,7 +6854,7 @@
         <v>293</v>
       </c>
       <c r="C141" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -4830,7 +6865,7 @@
         <v>294</v>
       </c>
       <c r="C142" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -4841,7 +6876,7 @@
         <v>295</v>
       </c>
       <c r="C143" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -4852,7 +6887,7 @@
         <v>296</v>
       </c>
       <c r="C144" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -4863,7 +6898,7 @@
         <v>297</v>
       </c>
       <c r="C145" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -4874,7 +6909,7 @@
         <v>298</v>
       </c>
       <c r="C146" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -4885,7 +6920,7 @@
         <v>299</v>
       </c>
       <c r="C147" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -4896,7 +6931,7 @@
         <v>300</v>
       </c>
       <c r="C148" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -4907,7 +6942,7 @@
         <v>301</v>
       </c>
       <c r="C149" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -4918,7 +6953,7 @@
         <v>302</v>
       </c>
       <c r="C150" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -4929,7 +6964,7 @@
         <v>303</v>
       </c>
       <c r="C151" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -4940,7 +6975,7 @@
         <v>304</v>
       </c>
       <c r="C152" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -4951,7 +6986,7 @@
         <v>305</v>
       </c>
       <c r="C153" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -4962,7 +6997,7 @@
         <v>306</v>
       </c>
       <c r="C154" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -4973,7 +7008,7 @@
         <v>307</v>
       </c>
       <c r="C155" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -4984,7 +7019,7 @@
         <v>308</v>
       </c>
       <c r="C156" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -4995,7 +7030,7 @@
         <v>309</v>
       </c>
       <c r="C157" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -5006,7 +7041,7 @@
         <v>310</v>
       </c>
       <c r="C158" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -5017,7 +7052,7 @@
         <v>311</v>
       </c>
       <c r="C159" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -5028,7 +7063,7 @@
         <v>312</v>
       </c>
       <c r="C160" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -5039,7 +7074,7 @@
         <v>313</v>
       </c>
       <c r="C161" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -5050,7 +7085,7 @@
         <v>314</v>
       </c>
       <c r="C162" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -5061,7 +7096,7 @@
         <v>315</v>
       </c>
       <c r="C163" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -5072,7 +7107,7 @@
         <v>316</v>
       </c>
       <c r="C164" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -5083,7 +7118,7 @@
         <v>317</v>
       </c>
       <c r="C165" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -5094,7 +7129,7 @@
         <v>318</v>
       </c>
       <c r="C166" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
   </sheetData>
@@ -5103,7 +7138,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
